--- a/2026-10-17/2026-10-17-mixed.xlsx
+++ b/2026-10-17/2026-10-17-mixed.xlsx
@@ -59,7 +59,7 @@
     <t>실행 시각 (KST)</t>
   </si>
   <si>
-    <t>2026-10-17 02:43</t>
+    <t>2026-10-17 04:21</t>
   </si>
   <si>
     <t>환경</t>
@@ -71,7 +71,7 @@
     <t>코드 버전</t>
   </si>
   <si>
-    <t>LP 7f010fa · GP 3315740</t>
+    <t>LP fd9a067 · GP a45c340</t>
   </si>
   <si>
     <t>데이터</t>
@@ -1202,7 +1202,7 @@
     <t>GP 공지 수신자 목록에서 하늘연금 확인 시각이 찍힌다</t>
   </si>
   <si>
-    <t>200 gp_sync sent · GP 2026-10-16T17:40:46.663113+00:00</t>
+    <t>200 gp_sync sent · GP 2026-10-16T19:19:08.803903+00:00</t>
   </si>
   <si>
     <t>Q6-3</t>
